--- a/artfynd/S 13-2026 artfynd.xlsx
+++ b/artfynd/S 13-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440189</v>
       </c>
       <c r="B2" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 13-2026 artfynd.xlsx
+++ b/artfynd/S 13-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136440189</v>
       </c>
       <c r="B2" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 13-2026 artfynd.xlsx
+++ b/artfynd/S 13-2026 artfynd.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jennifer Gao, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
